--- a/حركات الشركات للأسنان - جديد/JFZ_Transactions.xlsx
+++ b/حركات الشركات للأسنان - جديد/JFZ_Transactions.xlsx
@@ -1,45 +1,138 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Omar\waad_temp_website\حركات الشركات للأسنان - جديد\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{934FA600-FD1B-487D-95BC-59F74F5265D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="الاسنان" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="34">
+  <si>
+    <t>اسم المريض</t>
+  </si>
+  <si>
+    <t xml:space="preserve">رقم التأمين </t>
+  </si>
+  <si>
+    <t xml:space="preserve">رقم الموافقة </t>
+  </si>
+  <si>
+    <t>القيمة المالية</t>
+  </si>
+  <si>
+    <t>التاريخ</t>
+  </si>
+  <si>
+    <t>ملاحظات</t>
+  </si>
+  <si>
+    <t>المرفق الصحي</t>
+  </si>
+  <si>
+    <t>نسمة سالم عبدالله ارحيم</t>
+  </si>
+  <si>
+    <t>JFZ202533430D1</t>
+  </si>
+  <si>
+    <t>JFZ001</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>مركز فينيسيا - اسنان</t>
+  </si>
+  <si>
+    <t>سالم حسين محمد</t>
+  </si>
+  <si>
+    <t>JFZ202534348F1</t>
+  </si>
+  <si>
+    <t>JFZ002</t>
+  </si>
+  <si>
+    <t>مركز زركون - اسنان</t>
+  </si>
+  <si>
+    <t>رقية فضل الله عيسي</t>
+  </si>
+  <si>
+    <t>JFZ202532141H1</t>
+  </si>
+  <si>
+    <t>JFZ003</t>
+  </si>
+  <si>
+    <t>القذافي حمد عبدالعزيز العشيبي</t>
+  </si>
+  <si>
+    <t>JFZ2025</t>
+  </si>
+  <si>
+    <t>JFZ004</t>
+  </si>
+  <si>
+    <t>خالد عبدالله ابريك الطشاني</t>
+  </si>
+  <si>
+    <t>JFZ202531588</t>
+  </si>
+  <si>
+    <t>JFZ005</t>
+  </si>
+  <si>
+    <t>مركز الامل - اسنان</t>
+  </si>
+  <si>
+    <t>وجدان عبدالرازق بوشعالة</t>
+  </si>
+  <si>
+    <t>JFZ202533519W</t>
+  </si>
+  <si>
+    <t>JFZ006</t>
+  </si>
+  <si>
+    <t>مركز اوبال - اسنان</t>
+  </si>
+  <si>
+    <t>حسن اكريم عمر موسي</t>
+  </si>
+  <si>
+    <t>JFZ202531697</t>
+  </si>
+  <si>
+    <t>JFZ007</t>
+  </si>
+  <si>
+    <t>صيدلية دار الحياة</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -65,13 +158,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,343 +497,206 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.83203125" customWidth="1"/>
-    <col min="2" max="2" width="22.83203125" customWidth="1"/>
-    <col min="3" max="3" width="15.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="25.83203125" customWidth="1"/>
-    <col min="7" max="7" width="35.83203125" customWidth="1"/>
+    <col min="1" max="1" width="35.81640625" customWidth="1"/>
+    <col min="2" max="2" width="22.81640625" customWidth="1"/>
+    <col min="3" max="3" width="15.81640625" customWidth="1"/>
+    <col min="4" max="5" width="14.81640625" customWidth="1"/>
+    <col min="6" max="6" width="25.81640625" customWidth="1"/>
+    <col min="7" max="7" width="35.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>اسم المريض</v>
-      </c>
-      <c r="B1" t="str">
-        <v xml:space="preserve">رقم التأمين </v>
-      </c>
-      <c r="C1" t="str">
-        <v xml:space="preserve">رقم الموافقة </v>
-      </c>
-      <c r="D1" t="str">
-        <v>القيمة المالية</v>
-      </c>
-      <c r="E1" t="str">
-        <v>التاريخ</v>
-      </c>
-      <c r="F1" t="str">
-        <v>ملاحظات</v>
-      </c>
-      <c r="G1" t="str">
-        <v>المرفق الصحي</v>
+    <row r="1" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>نسمة سالم عبدالله ارحيم</v>
-      </c>
-      <c r="B2" t="str">
-        <v>JFZ202533430D1</v>
-      </c>
-      <c r="C2" t="str">
-        <v>JFZ001</v>
+    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
       </c>
       <c r="D2">
         <v>120</v>
       </c>
-      <c r="E2" t="str">
-        <v/>
-      </c>
-      <c r="F2" t="str">
-        <v/>
-      </c>
-      <c r="G2" t="str">
-        <v>مركز فينيسيا - اسنان</v>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>سالم حسين محمد</v>
-      </c>
-      <c r="B3" t="str">
-        <v>JFZ202534348F1</v>
-      </c>
-      <c r="C3" t="str">
-        <v>JFZ002</v>
+    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
       </c>
       <c r="D3">
         <v>2775</v>
       </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v>مركز زركون - اسنان</v>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>رقية فضل الله عيسي</v>
-      </c>
-      <c r="B4" t="str">
-        <v>JFZ202532141H1</v>
-      </c>
-      <c r="C4" t="str">
-        <v>JFZ003</v>
+    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
       </c>
       <c r="D4">
         <v>547.5</v>
       </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v>مركز فينيسيا - اسنان</v>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>القذافي حمد عبدالعزيز العشيبي</v>
-      </c>
-      <c r="B5" t="str">
-        <v>JFZ2025</v>
-      </c>
-      <c r="C5" t="str">
-        <v>JFZ004</v>
+    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
       </c>
       <c r="D5">
         <v>6750</v>
       </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v>مركز فينيسيا - اسنان</v>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>خالد عبدالله ابريك الطشاني</v>
-      </c>
-      <c r="B6" t="str">
-        <v>JFZ202531588</v>
-      </c>
-      <c r="C6" t="str">
-        <v>JFZ005</v>
+    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
       </c>
       <c r="D6">
         <v>195</v>
       </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v>مركز الامل - اسنان</v>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>وجدان عبدالرازق بوشعالة</v>
-      </c>
-      <c r="B7" t="str">
-        <v>JFZ202533519W</v>
-      </c>
-      <c r="C7" t="str">
-        <v>JFZ006</v>
+    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>28</v>
       </c>
       <c r="D7">
         <v>625</v>
       </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v>مركز اوبال - اسنان</v>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>حسن اكريم عمر موسي</v>
-      </c>
-      <c r="B8" t="str">
-        <v>JFZ202531697</v>
-      </c>
-      <c r="C8" t="str">
-        <v>JFZ007</v>
+    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>32</v>
       </c>
       <c r="D8">
         <v>406</v>
       </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v>صيدلية دار الحياة</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v/>
-      </c>
-      <c r="B9" t="str">
-        <v>JFZ2025</v>
-      </c>
-      <c r="C9" t="str">
-        <v>JFZ008</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v/>
-      </c>
-      <c r="B10" t="str">
-        <v>JFZ2025</v>
-      </c>
-      <c r="C10" t="str">
-        <v>JFZ009</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v/>
-      </c>
-      <c r="B11" t="str">
-        <v>JFZ2025</v>
-      </c>
-      <c r="C11" t="str">
-        <v>JFZ010</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v/>
-      </c>
-      <c r="B12" t="str">
-        <v>JFZ2025</v>
-      </c>
-      <c r="C12" t="str">
-        <v>JFZ011</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v/>
-      </c>
-      <c r="B13" t="str">
-        <v>JFZ2025</v>
-      </c>
-      <c r="C13" t="str">
-        <v>JFZ012</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v/>
-      </c>
-      <c r="B14" t="str">
-        <v>JFZ2025</v>
-      </c>
-      <c r="C14" t="str">
-        <v>JFZ013</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14" t="str">
-        <v/>
-      </c>
-      <c r="F14" t="str">
-        <v/>
-      </c>
-      <c r="G14" t="str">
-        <v/>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G14"/>
+    <ignoredError sqref="A1:G8" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>